--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5285" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5285" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -638,6 +638,11 @@
     <t>FR Core Organization Short Name Extension</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -653,6 +658,10 @@
   </si>
   <si>
     <t>FR Core Organization Description Extension</t>
+  </si>
+  <si>
+    <t>Description textuelle d'une organisation
+Organization description</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -4354,7 +4363,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4414,7 +4423,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -4434,13 +4443,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -4462,13 +4471,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4528,7 +4537,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -4548,13 +4557,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4576,13 +4585,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4662,10 +4671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4691,16 +4700,16 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4749,7 +4758,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4778,10 +4787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4804,17 +4813,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4851,10 +4860,10 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
@@ -4863,7 +4872,7 @@
         <v>115</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4872,30 +4881,30 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5004,10 +5013,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5118,10 +5127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5147,16 +5156,16 @@
         <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5181,11 +5190,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5203,7 +5212,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5221,7 +5230,7 @@
         <v>191</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5232,10 +5241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5258,19 +5267,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5299,7 +5308,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5317,7 +5326,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5332,10 +5341,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5346,10 +5355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5375,16 +5384,16 @@
         <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5397,7 +5406,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -5433,7 +5442,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5448,13 +5457,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5462,10 +5471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5491,13 +5500,13 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5511,7 +5520,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -5547,7 +5556,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5562,13 +5571,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5576,10 +5585,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5602,13 +5611,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5659,7 +5668,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5674,13 +5683,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5688,10 +5697,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5714,16 +5723,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5773,7 +5782,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5788,13 +5797,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5802,13 +5811,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5830,17 +5839,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5889,7 +5898,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5898,30 +5907,30 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6030,10 +6039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6144,10 +6153,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6173,16 +6182,16 @@
         <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6192,7 +6201,7 @@
         <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>78</v>
@@ -6207,13 +6216,13 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6231,7 +6240,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6249,7 +6258,7 @@
         <v>191</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6260,10 +6269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6286,19 +6295,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6308,7 +6317,7 @@
         <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>78</v>
@@ -6326,10 +6335,10 @@
         <v>150</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -6347,7 +6356,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6362,10 +6371,10 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6376,10 +6385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6405,16 +6414,16 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6424,10 +6433,10 @@
         <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>78</v>
@@ -6463,7 +6472,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6478,13 +6487,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6492,10 +6501,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6521,13 +6530,13 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6541,7 +6550,7 @@
         <v>78</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>78</v>
@@ -6577,7 +6586,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6592,13 +6601,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6606,10 +6615,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6632,13 +6641,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6689,7 +6698,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6704,13 +6713,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6718,10 +6727,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6744,16 +6753,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6803,7 +6812,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6818,13 +6827,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6832,13 +6841,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
@@ -6860,17 +6869,17 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6919,7 +6928,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6928,30 +6937,30 @@
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7060,10 +7069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7174,10 +7183,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7203,16 +7212,16 @@
         <v>168</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7237,13 +7246,13 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7261,7 +7270,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7279,7 +7288,7 @@
         <v>191</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7290,10 +7299,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7316,19 +7325,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7338,7 +7347,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7356,10 +7365,10 @@
         <v>150</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7377,7 +7386,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7392,10 +7401,10 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7406,10 +7415,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7435,16 +7444,16 @@
         <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7454,10 +7463,10 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>78</v>
@@ -7493,7 +7502,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7508,13 +7517,13 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7522,10 +7531,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7551,13 +7560,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7571,7 +7580,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7607,7 +7616,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7622,13 +7631,13 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7636,10 +7645,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7662,13 +7671,13 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7719,7 +7728,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7734,13 +7743,13 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7748,10 +7757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7774,16 +7783,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7833,7 +7842,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7848,13 +7857,13 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7862,13 +7871,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -7890,17 +7899,17 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7949,7 +7958,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7958,30 +7967,30 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8090,10 +8099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8204,10 +8213,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8233,16 +8242,16 @@
         <v>168</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8267,13 +8276,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8291,7 +8300,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8309,7 +8318,7 @@
         <v>191</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8320,10 +8329,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8346,19 +8355,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8368,7 +8377,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8386,10 +8395,10 @@
         <v>150</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8407,7 +8416,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8422,10 +8431,10 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8436,10 +8445,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8465,16 +8474,16 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8484,10 +8493,10 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8523,7 +8532,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8538,13 +8547,13 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8552,10 +8561,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8581,13 +8590,13 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8601,7 +8610,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8637,7 +8646,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8652,13 +8661,13 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8666,10 +8675,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8692,13 +8701,13 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8749,7 +8758,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8764,13 +8773,13 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8778,10 +8787,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8804,16 +8813,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8863,7 +8872,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8878,13 +8887,13 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8892,13 +8901,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -8920,17 +8929,17 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8979,7 +8988,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8988,30 +8997,30 @@
         <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9120,10 +9129,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9234,10 +9243,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9263,16 +9272,16 @@
         <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9297,13 +9306,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9321,7 +9330,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9339,7 +9348,7 @@
         <v>191</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9350,10 +9359,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9376,19 +9385,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9416,10 +9425,10 @@
         <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9437,7 +9446,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9452,10 +9461,10 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9466,10 +9475,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9578,10 +9587,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9692,10 +9701,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9721,16 +9730,16 @@
         <v>146</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9779,7 +9788,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9794,10 +9803,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9808,10 +9817,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9920,10 +9929,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10034,10 +10043,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10063,16 +10072,16 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10082,7 +10091,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10121,7 +10130,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10136,10 +10145,10 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10150,10 +10159,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10179,13 +10188,13 @@
         <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10235,7 +10244,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10250,10 +10259,10 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10264,10 +10273,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10293,14 +10302,14 @@
         <v>168</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10349,7 +10358,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10364,10 +10373,10 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10378,10 +10387,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10407,14 +10416,14 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10463,7 +10472,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10478,10 +10487,10 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10492,10 +10501,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10518,19 +10527,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10579,7 +10588,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10594,10 +10603,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10608,10 +10617,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10637,16 +10646,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10695,7 +10704,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10710,10 +10719,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10724,10 +10733,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10753,16 +10762,16 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10772,10 +10781,10 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>78</v>
@@ -10811,7 +10820,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10826,13 +10835,13 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10840,10 +10849,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10869,13 +10878,13 @@
         <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10889,7 +10898,7 @@
         <v>78</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>78</v>
@@ -10925,7 +10934,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10940,13 +10949,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10954,10 +10963,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10980,13 +10989,13 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11037,7 +11046,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11052,13 +11061,13 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11066,10 +11075,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11092,16 +11101,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11151,7 +11160,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11166,13 +11175,13 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11180,13 +11189,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11208,17 +11217,17 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11267,7 +11276,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11276,30 +11285,30 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11408,10 +11417,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11522,10 +11531,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11551,16 +11560,16 @@
         <v>168</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11585,13 +11594,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11609,7 +11618,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11627,7 +11636,7 @@
         <v>191</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11638,10 +11647,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11664,19 +11673,19 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11686,7 +11695,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11704,10 +11713,10 @@
         <v>150</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11725,7 +11734,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11740,10 +11749,10 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11754,10 +11763,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11783,16 +11792,16 @@
         <v>130</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11802,10 +11811,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -11841,7 +11850,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11856,13 +11865,13 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11870,10 +11879,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11899,13 +11908,13 @@
         <v>102</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11919,7 +11928,7 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -11955,7 +11964,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11970,13 +11979,13 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -11984,10 +11993,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12010,13 +12019,13 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12067,7 +12076,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12082,13 +12091,13 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12096,10 +12105,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12122,16 +12131,16 @@
         <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12181,7 +12190,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12196,13 +12205,13 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12210,10 +12219,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12236,70 +12245,70 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M88" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q88" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="R88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12314,24 +12323,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12354,19 +12363,19 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12394,16 +12403,16 @@
         <v>158</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -12413,7 +12422,7 @@
         <v>115</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12428,27 +12437,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12470,19 +12479,19 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12507,11 +12516,11 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12529,7 +12538,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12544,24 +12553,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12670,10 +12679,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12784,10 +12793,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12813,16 +12822,16 @@
         <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12871,7 +12880,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12886,10 +12895,10 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12900,10 +12909,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13012,10 +13021,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13126,10 +13135,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13155,16 +13164,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13213,7 +13222,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13228,10 +13237,10 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13242,10 +13251,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13271,13 +13280,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13327,7 +13336,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13342,10 +13351,10 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13356,10 +13365,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13385,14 +13394,14 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13441,7 +13450,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13456,10 +13465,10 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13470,10 +13479,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13499,14 +13508,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13555,7 +13564,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13570,10 +13579,10 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13584,10 +13593,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13610,19 +13619,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13671,7 +13680,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13686,10 +13695,10 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13700,10 +13709,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13729,16 +13738,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13787,7 +13796,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13802,10 +13811,10 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13816,13 +13825,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13844,19 +13853,19 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13881,11 +13890,11 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13903,7 +13912,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13918,24 +13927,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14044,10 +14053,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14158,10 +14167,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14187,16 +14196,16 @@
         <v>146</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14245,7 +14254,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14260,10 +14269,10 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14274,10 +14283,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14386,10 +14395,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14500,10 +14509,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14529,16 +14538,16 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14587,7 +14596,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14602,10 +14611,10 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14616,10 +14625,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14645,13 +14654,13 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14701,7 +14710,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14716,10 +14725,10 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14730,10 +14739,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14759,14 +14768,14 @@
         <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14815,7 +14824,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14830,10 +14839,10 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14844,10 +14853,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14873,14 +14882,14 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14929,7 +14938,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14944,10 +14953,10 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14958,10 +14967,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14984,19 +14993,19 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15045,7 +15054,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15060,10 +15069,10 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15074,10 +15083,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15103,16 +15112,16 @@
         <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15161,7 +15170,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15176,10 +15185,10 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15190,13 +15199,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
@@ -15218,19 +15227,19 @@
         <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15255,11 +15264,11 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15277,7 +15286,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15292,24 +15301,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15418,10 +15427,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15532,10 +15541,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15561,16 +15570,16 @@
         <v>146</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15619,7 +15628,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15634,10 +15643,10 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15648,10 +15657,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15760,10 +15769,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15874,10 +15883,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15903,16 +15912,16 @@
         <v>130</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -15961,7 +15970,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15976,10 +15985,10 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15990,10 +15999,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16019,13 +16028,13 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16075,7 +16084,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16090,10 +16099,10 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16104,10 +16113,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16133,14 +16142,14 @@
         <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16189,7 +16198,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16204,10 +16213,10 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -16218,10 +16227,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16247,14 +16256,14 @@
         <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16303,7 +16312,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16318,10 +16327,10 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -16332,10 +16341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16358,19 +16367,19 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16419,7 +16428,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16434,10 +16443,10 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16448,10 +16457,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16477,16 +16486,16 @@
         <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16535,7 +16544,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16550,10 +16559,10 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
@@ -16564,10 +16573,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16593,16 +16602,16 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16651,7 +16660,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16660,19 +16669,19 @@
         <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16680,10 +16689,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16709,16 +16718,16 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16767,7 +16776,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16785,7 +16794,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16796,10 +16805,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16822,19 +16831,19 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16883,7 +16892,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16892,19 +16901,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16912,10 +16921,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16938,19 +16947,19 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16999,7 +17008,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17008,19 +17017,19 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17028,10 +17037,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17054,17 +17063,17 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17113,7 +17122,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17128,10 +17137,10 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>106</v>
@@ -17142,10 +17151,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17254,10 +17263,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17368,10 +17377,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17397,13 +17406,13 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17453,7 +17462,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17462,7 +17471,7 @@
         <v>88</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17482,10 +17491,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17511,13 +17520,13 @@
         <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17547,7 +17556,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17565,7 +17574,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17594,10 +17603,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17620,16 +17629,16 @@
         <v>89</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17679,7 +17688,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17697,7 +17706,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -17708,10 +17717,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17737,13 +17746,13 @@
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17793,7 +17802,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17822,10 +17831,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17848,19 +17857,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17909,7 +17918,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17927,7 +17936,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17938,10 +17947,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18050,10 +18059,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18164,14 +18173,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18193,16 +18202,16 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -18251,7 +18260,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18280,10 +18289,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18306,17 +18315,17 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18344,10 +18353,10 @@
         <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
@@ -18365,7 +18374,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18383,7 +18392,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18394,10 +18403,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18420,17 +18429,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18479,7 +18488,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18494,10 +18503,10 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18508,10 +18517,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18534,17 +18543,17 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18593,7 +18602,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18608,10 +18617,10 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
@@ -18622,10 +18631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18648,17 +18657,17 @@
         <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -18707,7 +18716,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18722,10 +18731,10 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -18736,10 +18745,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18762,17 +18771,17 @@
         <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18821,7 +18830,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
